--- a/rules/CORE-000542/positive/01/data/unit-test-coreid-FB3102-positive.xlsx
+++ b/rules/CORE-000542/positive/01/data/unit-test-coreid-FB3102-positive.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rich/Documents/github/core-contributor/rules/CORE-000542/positive/01/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{402E9543-9DCD-114A-800D-9CD98E11125A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EDFB58E-1A4E-1F45-A7A2-904A3BEB1B3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Library" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="354" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="153">
   <si>
     <t>Product</t>
   </si>
@@ -482,6 +482,9 @@
   </si>
   <si>
     <t>1.00</t>
+  </si>
+  <si>
+    <t>000</t>
   </si>
 </sst>
 </file>
@@ -1304,8 +1307,8 @@
       <c r="H9" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="I9" s="2">
-        <v>0</v>
+      <c r="I9" s="5" t="s">
+        <v>152</v>
       </c>
       <c r="J9" s="2">
         <v>0</v>
